--- a/Quiniela_Mundial_2026_Totalmente_Corregida (1).xlsx
+++ b/Quiniela_Mundial_2026_Totalmente_Corregida (1).xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +86,11 @@
       <color rgb="00333333"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -142,8 +145,14 @@
         <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+        <bgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -202,11 +211,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,6 +309,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6165,13 +6191,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="10" min="2" max="2"/>
-    <col width="9.140625" customWidth="1" style="16" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="16" min="5" max="5"/>
-    <col width="20" customWidth="1" style="10" min="6" max="7"/>
+    <col width="6" customWidth="1" style="16" min="3" max="3"/>
+    <col width="6" customWidth="1" style="10" min="4" max="4"/>
+    <col width="3" customWidth="1" style="16" min="5" max="5"/>
+    <col width="6" customWidth="1" style="10" min="6" max="7"/>
+    <col width="6" customWidth="1" style="10" min="7" max="7"/>
+    <col width="18" customWidth="1" style="10" min="8" max="8"/>
+    <col width="18" customWidth="1" style="10" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6205,29 +6235,34 @@
           <t>Goles</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Pen.</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Pen.</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Goles</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Equipo B</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Clasifica</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -6244,20 +6279,22 @@
       <c r="C6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f>Backend!C3</f>
         <v/>
       </c>
-      <c r="G6">
-        <f>IF(AND(ISNUMBER(C6),ISNUMBER(E6)),IF(C6&gt;E6,B6,F6),"")</f>
+      <c r="I6">
+        <f>IF(OR(C6="", G6=""), "", IF(C6&gt;G6, B6, IF(G6&gt;C6, H6, IF(D6&gt;F6, B6, IF(F6&gt;D6, H6, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6274,20 +6311,22 @@
       <c r="C7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <f>Backend!C4</f>
         <v/>
       </c>
-      <c r="G7">
-        <f>IF(AND(ISNUMBER(C7),ISNUMBER(E7)),IF(C7&gt;E7,B7,F7),"")</f>
+      <c r="I7">
+        <f>IF(OR(C7="", G7=""), "", IF(C7&gt;G7, B7, IF(G7&gt;C7, H7, IF(D7&gt;F7, B7, IF(F7&gt;D7, H7, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6304,20 +6343,22 @@
       <c r="C8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F8">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 5, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>IF(AND(ISNUMBER(C8),ISNUMBER(E8)),IF(C8&gt;E8,B8,F8),"")</f>
+      <c r="H8">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 5, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(OR(C8="", G8=""), "", IF(C8&gt;G8, B8, IF(G8&gt;C8, H8, IF(D8&gt;F8, B8, IF(F8&gt;D8, H8, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6334,20 +6375,22 @@
       <c r="C9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F9">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 7, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>IF(AND(ISNUMBER(C9),ISNUMBER(E9)),IF(C9&gt;E9,B9,F9),"")</f>
+      <c r="H9">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 7, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(OR(C9="", G9=""), "", IF(C9&gt;G9, B9, IF(G9&gt;C9, H9, IF(D9&gt;F9, B9, IF(F9&gt;D9, H9, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6364,20 +6407,22 @@
       <c r="C10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <f>Backend!C7</f>
         <v/>
       </c>
-      <c r="G10">
-        <f>IF(AND(ISNUMBER(C10),ISNUMBER(E10)),IF(C10&gt;E10,B10,F10),"")</f>
+      <c r="I10">
+        <f>IF(OR(C10="", G10=""), "", IF(C10&gt;G10, B10, IF(G10&gt;C10, H10, IF(D10&gt;F10, B10, IF(F10&gt;D10, H10, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6394,20 +6439,22 @@
       <c r="C11" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <f>Backend!C10</f>
         <v/>
       </c>
-      <c r="G11">
-        <f>IF(AND(ISNUMBER(C11),ISNUMBER(E11)),IF(C11&gt;E11,B11,F11),"")</f>
+      <c r="I11">
+        <f>IF(OR(C11="", G11=""), "", IF(C11&gt;G11, B11, IF(G11&gt;C11, H11, IF(D11&gt;F11, B11, IF(F11&gt;D11, H11, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6424,20 +6471,22 @@
       <c r="C12" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F12">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 2, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>IF(AND(ISNUMBER(C12),ISNUMBER(E12)),IF(C12&gt;E12,B12,F12),"")</f>
+      <c r="H12">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 2, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(OR(C12="", G12=""), "", IF(C12&gt;G12, B12, IF(G12&gt;C12, H12, IF(D12&gt;F12, B12, IF(F12&gt;D12, H12, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6454,20 +6503,22 @@
       <c r="C13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F13">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 9, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>IF(AND(ISNUMBER(C13),ISNUMBER(E13)),IF(C13&gt;E13,B13,F13),"")</f>
+      <c r="H13">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 9, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(OR(C13="", G13=""), "", IF(C13&gt;G13, B13, IF(G13&gt;C13, H13, IF(D13&gt;F13, B13, IF(F13&gt;D13, H13, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6484,20 +6535,22 @@
       <c r="C14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F14">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 4, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>IF(AND(ISNUMBER(C14),ISNUMBER(E14)),IF(C14&gt;E14,B14,F14),"")</f>
+      <c r="H14">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 4, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(OR(C14="", G14=""), "", IF(C14&gt;G14, B14, IF(G14&gt;C14, H14, IF(D14&gt;F14, B14, IF(F14&gt;D14, H14, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6514,20 +6567,22 @@
       <c r="C15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F15">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 6, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>IF(AND(ISNUMBER(C15),ISNUMBER(E15)),IF(C15&gt;E15,B15,F15),"")</f>
+      <c r="H15">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 6, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(OR(C15="", G15=""), "", IF(C15&gt;G15, B15, IF(G15&gt;C15, H15, IF(D15&gt;F15, B15, IF(F15&gt;D15, H15, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6544,20 +6599,22 @@
       <c r="C16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <f>Backend!C13</f>
         <v/>
       </c>
-      <c r="G16">
-        <f>IF(AND(ISNUMBER(C16),ISNUMBER(E16)),IF(C16&gt;E16,B16,F16),"")</f>
+      <c r="I16">
+        <f>IF(OR(C16="", G16=""), "", IF(C16&gt;G16, B16, IF(G16&gt;C16, H16, IF(D16&gt;F16, B16, IF(F16&gt;D16, H16, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6574,20 +6631,22 @@
       <c r="C17" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <f>Backend!C11</f>
         <v/>
       </c>
-      <c r="G17">
-        <f>IF(AND(ISNUMBER(C17),ISNUMBER(E17)),IF(C17&gt;E17,B17,F17),"")</f>
+      <c r="I17">
+        <f>IF(OR(C17="", G17=""), "", IF(C17&gt;G17, B17, IF(G17&gt;C17, H17, IF(D17&gt;F17, B17, IF(F17&gt;D17, H17, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6604,20 +6663,22 @@
       <c r="C18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F18">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 3, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>IF(AND(ISNUMBER(C18),ISNUMBER(E18)),IF(C18&gt;E18,B18,F18),"")</f>
+      <c r="H18">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 3, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(OR(C18="", G18=""), "", IF(C18&gt;G18, B18, IF(G18&gt;C18, H18, IF(D18&gt;F18, B18, IF(F18&gt;D18, H18, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6634,20 +6695,22 @@
       <c r="C19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F19">
-        <f>INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 8, FALSE), Backend!$B$16:$B$23, 0))</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>IF(AND(ISNUMBER(C19),ISNUMBER(E19)),IF(C19&gt;E19,B19,F19),"")</f>
+      <c r="H19">
+        <f>IFERROR(INDEX(Backend!$C$16:$C$23, MATCH(VLOOKUP(Backend!$D$29, MatrizTerceros!$A$1:$I$495, 8, FALSE), Backend!$B$16:$B$23, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(OR(C19="", G19=""), "", IF(C19&gt;G19, B19, IF(G19&gt;C19, H19, IF(D19&gt;F19, B19, IF(F19&gt;D19, H19, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6664,20 +6727,22 @@
       <c r="C20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <f>Backend!C9</f>
         <v/>
       </c>
-      <c r="G20">
-        <f>IF(AND(ISNUMBER(C20),ISNUMBER(E20)),IF(C20&gt;E20,B20,F20),"")</f>
+      <c r="I20">
+        <f>IF(OR(C20="", G20=""), "", IF(C20&gt;G20, B20, IF(G20&gt;C20, H20, IF(D20&gt;F20, B20, IF(F20&gt;D20, H20, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6694,20 +6759,22 @@
       <c r="C21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <f>Backend!C8</f>
         <v/>
       </c>
-      <c r="G21">
-        <f>IF(AND(ISNUMBER(C21),ISNUMBER(E21)),IF(C21&gt;E21,B21,F21),"")</f>
+      <c r="I21">
+        <f>IF(OR(C21="", G21=""), "", IF(C21&gt;G21, B21, IF(G21&gt;C21, H21, IF(D21&gt;F21, B21, IF(F21&gt;D21, H21, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6725,26 +6792,28 @@
         </is>
       </c>
       <c r="B25">
-        <f>G6</f>
+        <f>I6</f>
         <v/>
       </c>
       <c r="C25" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F25">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>IF(AND(ISNUMBER(C25),ISNUMBER(E25)),IF(C25&gt;E25,B25,F25),"")</f>
+      <c r="H25">
+        <f>I7</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(OR(C25="", G25=""), "", IF(C25&gt;G25, B25, IF(G25&gt;C25, H25, IF(D25&gt;F25, B25, IF(F25&gt;D25, H25, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6755,26 +6824,28 @@
         </is>
       </c>
       <c r="B26">
-        <f>G8</f>
+        <f>I8</f>
         <v/>
       </c>
       <c r="C26" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F26">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>IF(AND(ISNUMBER(C26),ISNUMBER(E26)),IF(C26&gt;E26,B26,F26),"")</f>
+      <c r="H26">
+        <f>I9</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(OR(C26="", G26=""), "", IF(C26&gt;G26, B26, IF(G26&gt;C26, H26, IF(D26&gt;F26, B26, IF(F26&gt;D26, H26, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6785,26 +6856,28 @@
         </is>
       </c>
       <c r="B27">
-        <f>G10</f>
+        <f>I10</f>
         <v/>
       </c>
       <c r="C27" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F27">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="G27">
-        <f>IF(AND(ISNUMBER(C27),ISNUMBER(E27)),IF(C27&gt;E27,B27,F27),"")</f>
+      <c r="H27">
+        <f>I11</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(OR(C27="", G27=""), "", IF(C27&gt;G27, B27, IF(G27&gt;C27, H27, IF(D27&gt;F27, B27, IF(F27&gt;D27, H27, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6815,26 +6888,28 @@
         </is>
       </c>
       <c r="B28">
-        <f>G12</f>
+        <f>I12</f>
         <v/>
       </c>
       <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F28">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(AND(ISNUMBER(C28),ISNUMBER(E28)),IF(C28&gt;E28,B28,F28),"")</f>
+      <c r="H28">
+        <f>I13</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(OR(C28="", G28=""), "", IF(C28&gt;G28, B28, IF(G28&gt;C28, H28, IF(D28&gt;F28, B28, IF(F28&gt;D28, H28, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6845,26 +6920,28 @@
         </is>
       </c>
       <c r="B29">
-        <f>G14</f>
+        <f>I14</f>
         <v/>
       </c>
       <c r="C29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F29">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="G29">
-        <f>IF(AND(ISNUMBER(C29),ISNUMBER(E29)),IF(C29&gt;E29,B29,F29),"")</f>
+      <c r="H29">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(OR(C29="", G29=""), "", IF(C29&gt;G29, B29, IF(G29&gt;C29, H29, IF(D29&gt;F29, B29, IF(F29&gt;D29, H29, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6875,26 +6952,28 @@
         </is>
       </c>
       <c r="B30">
-        <f>G16</f>
+        <f>I16</f>
         <v/>
       </c>
       <c r="C30" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F30">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="G30">
-        <f>IF(AND(ISNUMBER(C30),ISNUMBER(E30)),IF(C30&gt;E30,B30,F30),"")</f>
+      <c r="H30">
+        <f>I17</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(OR(C30="", G30=""), "", IF(C30&gt;G30, B30, IF(G30&gt;C30, H30, IF(D30&gt;F30, B30, IF(F30&gt;D30, H30, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6905,26 +6984,28 @@
         </is>
       </c>
       <c r="B31">
-        <f>G18</f>
+        <f>I18</f>
         <v/>
       </c>
       <c r="C31" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F31">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="G31">
-        <f>IF(AND(ISNUMBER(C31),ISNUMBER(E31)),IF(C31&gt;E31,B31,F31),"")</f>
+      <c r="H31">
+        <f>I19</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>IF(OR(C31="", G31=""), "", IF(C31&gt;G31, B31, IF(G31&gt;C31, H31, IF(D31&gt;F31, B31, IF(F31&gt;D31, H31, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6935,26 +7016,28 @@
         </is>
       </c>
       <c r="B32">
-        <f>G20</f>
+        <f>I20</f>
         <v/>
       </c>
       <c r="C32" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F32">
-        <f>G21</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(AND(ISNUMBER(C32),ISNUMBER(E32)),IF(C32&gt;E32,B32,F32),"")</f>
+      <c r="H32">
+        <f>I21</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>IF(OR(C32="", G32=""), "", IF(C32&gt;G32, B32, IF(G32&gt;C32, H32, IF(D32&gt;F32, B32, IF(F32&gt;D32, H32, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -6962,21 +7045,19 @@
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="17" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="G33" s="17" t="n"/>
       <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="17" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="G34" s="17" t="n"/>
       <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" s="10">
       <c r="A35" s="21" t="inlineStr">
@@ -7001,29 +7082,24 @@
           <t>Goles</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>Goles</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>Equipo B</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>Clasifica</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -7034,26 +7110,28 @@
         </is>
       </c>
       <c r="B37">
-        <f>G25</f>
+        <f>I25</f>
         <v/>
       </c>
       <c r="C37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F37">
-        <f>G26</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>IF(AND(ISNUMBER(C37),ISNUMBER(E37)),IF(C37&gt;E37,B37,F37),"")</f>
+      <c r="H37">
+        <f>I26</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>IF(OR(C37="", G37=""), "", IF(C37&gt;G37, B37, IF(G37&gt;C37, H37, IF(D37&gt;F37, B37, IF(F37&gt;D37, H37, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7064,26 +7142,28 @@
         </is>
       </c>
       <c r="B38">
-        <f>G27</f>
+        <f>I27</f>
         <v/>
       </c>
       <c r="C38" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F38">
-        <f>G28</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>IF(AND(ISNUMBER(C38),ISNUMBER(E38)),IF(C38&gt;E38,B38,F38),"")</f>
+      <c r="H38">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>IF(OR(C38="", G38=""), "", IF(C38&gt;G38, B38, IF(G38&gt;C38, H38, IF(D38&gt;F38, B38, IF(F38&gt;D38, H38, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7094,26 +7174,28 @@
         </is>
       </c>
       <c r="B39">
-        <f>G29</f>
+        <f>I29</f>
         <v/>
       </c>
       <c r="C39" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F39">
-        <f>G30</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>IF(AND(ISNUMBER(C39),ISNUMBER(E39)),IF(C39&gt;E39,B39,F39),"")</f>
+      <c r="H39">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>IF(OR(C39="", G39=""), "", IF(C39&gt;G39, B39, IF(G39&gt;C39, H39, IF(D39&gt;F39, B39, IF(F39&gt;D39, H39, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7124,26 +7206,28 @@
         </is>
       </c>
       <c r="B40">
-        <f>G31</f>
+        <f>I31</f>
         <v/>
       </c>
       <c r="C40" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F40">
-        <f>G32</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>IF(AND(ISNUMBER(C40),ISNUMBER(E40)),IF(C40&gt;E40,B40,F40),"")</f>
+      <c r="H40">
+        <f>I32</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>IF(OR(C40="", G40=""), "", IF(C40&gt;G40, B40, IF(G40&gt;C40, H40, IF(D40&gt;F40, B40, IF(F40&gt;D40, H40, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7151,21 +7235,19 @@
       <c r="A41" s="7" t="n"/>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="17" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="G41" s="17" t="n"/>
       <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="17" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="G42" s="17" t="n"/>
       <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" s="10">
       <c r="A43" s="21" t="inlineStr">
@@ -7190,29 +7272,24 @@
           <t>Goles</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>Goles</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Equipo B</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>Clasifica</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -7223,26 +7300,28 @@
         </is>
       </c>
       <c r="B45">
-        <f>G37</f>
+        <f>I37</f>
         <v/>
       </c>
       <c r="C45" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="F45" s="31" t="n"/>
+      <c r="G45" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F45">
-        <f>G38</f>
-        <v/>
-      </c>
-      <c r="G45">
-        <f>IF(AND(ISNUMBER(C45),ISNUMBER(E45)),IF(C45&gt;E45,B45,F45),"")</f>
+      <c r="H45">
+        <f>I38</f>
+        <v/>
+      </c>
+      <c r="I45">
+        <f>IF(OR(C45="", G45=""), "", IF(C45&gt;G45, B45, IF(G45&gt;C45, H45, IF(D45&gt;F45, B45, IF(F45&gt;D45, H45, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7253,26 +7332,28 @@
         </is>
       </c>
       <c r="B46">
-        <f>G39</f>
+        <f>I39</f>
         <v/>
       </c>
       <c r="C46" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="31" t="n"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="F46" s="31" t="n"/>
+      <c r="G46" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F46">
-        <f>G40</f>
-        <v/>
-      </c>
-      <c r="G46">
-        <f>IF(AND(ISNUMBER(C46),ISNUMBER(E46)),IF(C46&gt;E46,B46,F46),"")</f>
+      <c r="H46">
+        <f>I40</f>
+        <v/>
+      </c>
+      <c r="I46">
+        <f>IF(OR(C46="", G46=""), "", IF(C46&gt;G46, B46, IF(G46&gt;C46, H46, IF(D46&gt;F46, B46, IF(F46&gt;D46, H46, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7280,21 +7361,19 @@
       <c r="A47" s="7" t="n"/>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="17" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="G47" s="17" t="n"/>
       <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="17" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="G48" s="17" t="n"/>
       <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" s="10">
       <c r="A49" s="21" t="inlineStr">
@@ -7319,29 +7398,24 @@
           <t>Goles</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>Goles</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>Equipo B</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>Clasifica</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -7352,26 +7426,28 @@
         </is>
       </c>
       <c r="B51">
-        <f>IF(C45&lt;E45,B45,IF(C45&gt;E45,F45,""))</f>
+        <f>IF(OR(C45="", G45=""), "", IF(C45&lt;G45, B45, IF(G45&lt;C45, H45, IF(D45&lt;F45, B45, IF(F45&lt;D45, H45, "")))))</f>
         <v/>
       </c>
       <c r="C51" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="F51" s="31" t="n"/>
+      <c r="G51" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F51">
-        <f>IF(C46&lt;E46,B46,IF(C46&gt;E46,F46,""))</f>
-        <v/>
-      </c>
-      <c r="G51">
-        <f>IF(AND(ISNUMBER(C51),ISNUMBER(E51)),IF(C51&gt;E51,B51,F51),"")</f>
+      <c r="H51">
+        <f>IF(OR(C46="", G46=""), "", IF(C46&lt;G46, B46, IF(G46&lt;C46, H46, IF(D46&lt;F46, B46, IF(F46&lt;D46, H46, "")))))</f>
+        <v/>
+      </c>
+      <c r="I51">
+        <f>IF(OR(C51="", G51=""), "", IF(C51&gt;G51, B51, IF(G51&gt;C51, H51, IF(D51&gt;F51, B51, IF(F51&gt;D51, H51, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7379,21 +7455,19 @@
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="17" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="G52" s="17" t="n"/>
       <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="17" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="7" t="n"/>
-      <c r="G53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="G53" s="17" t="n"/>
       <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1" s="10">
       <c r="A54" s="21" t="inlineStr">
@@ -7418,29 +7492,24 @@
           <t>Goles</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>Goles</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="H55" s="13" t="inlineStr">
         <is>
           <t>Equipo B</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>Clasifica</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -7451,26 +7520,28 @@
         </is>
       </c>
       <c r="B56">
-        <f>G45</f>
+        <f>I45</f>
         <v/>
       </c>
       <c r="C56" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="31" t="n"/>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E56" s="15" t="n">
+      <c r="F56" s="31" t="n"/>
+      <c r="G56" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F56">
-        <f>G46</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>IF(AND(ISNUMBER(C56),ISNUMBER(E56)),IF(C56&gt;E56,B56,F56),"")</f>
+      <c r="H56">
+        <f>I46</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>IF(OR(C56="", G56=""), "", IF(C56&gt;G56, B56, IF(G56&gt;C56, H56, IF(D56&gt;F56, B56, IF(F56&gt;D56, H56, "Faltan Penales")))))</f>
         <v/>
       </c>
     </row>
@@ -7478,21 +7549,19 @@
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="17" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="G57" s="17" t="n"/>
       <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="17" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="G58" s="17" t="n"/>
       <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
     </row>
     <row r="59" ht="18.75" customHeight="1" s="10">
       <c r="A59" s="21" t="inlineStr">
@@ -7508,12 +7577,11 @@
           <t>CAMPEÓN MUNDIAL 🏆</t>
         </is>
       </c>
-      <c r="F60" s="8">
-        <f>G56</f>
-        <v/>
-      </c>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="8">
+        <f>I56</f>
+        <v/>
+      </c>
+      <c r="I60" s="7" t="n"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="10">
       <c r="A61" s="7" t="n"/>
@@ -7522,12 +7590,11 @@
           <t>Subcampeón 🥈</t>
         </is>
       </c>
-      <c r="F61" s="8">
-        <f>IF(C56&lt;E56,B56,IF(C56&gt;E56,F56,""))</f>
-        <v/>
-      </c>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
+      <c r="H61" s="8">
+        <f>IF(OR(C56="", G56=""), "", IF(C56&lt;G56, B56, IF(G56&lt;C56, H56, IF(D56&lt;F56, B56, IF(F56&lt;D56, H56, "")))))</f>
+        <v/>
+      </c>
+      <c r="I61" s="7" t="n"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="10">
       <c r="A62" s="7" t="n"/>
@@ -7536,26 +7603,25 @@
           <t>Tercer Lugar 🥉</t>
         </is>
       </c>
-      <c r="F62" s="8">
-        <f>G51</f>
-        <v/>
-      </c>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="8">
+        <f>I51</f>
+        <v/>
+      </c>
+      <c r="I62" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
